--- a/grupos/4ASV - Estadisticos 20232.xlsx
+++ b/grupos/4ASV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="77">
   <si>
     <t>Materia</t>
   </si>
@@ -185,6 +185,12 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>Sanchez Hernández Raymundo</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -194,12 +200,6 @@
     <t>Urias Morales Alejandra</t>
   </si>
   <si>
-    <t>Sanchez Hernández Raymundo</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,10 +212,10 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
@@ -224,22 +224,10 @@
     <t>QUESADA</t>
   </si>
   <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>PAZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
@@ -248,19 +236,10 @@
     <t>OLGUIN</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>AARON</t>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
   </si>
   <si>
     <t>GAMALIEL</t>
@@ -269,16 +248,7 @@
     <t>JARED DE JESUS</t>
   </si>
   <si>
-    <t>ESTEPHANY</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
     <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -786,22 +756,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -822,22 +792,22 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>10</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -863,22 +833,22 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -899,16 +869,16 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -940,22 +910,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -976,19 +946,19 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>10</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1017,22 +987,22 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1053,22 +1023,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>10</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1094,22 +1064,22 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1130,19 +1100,19 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>10</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1171,22 +1141,22 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1207,22 +1177,22 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1248,22 +1218,22 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1284,7 +1254,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1299,7 +1269,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1325,22 +1295,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1361,22 +1331,22 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1402,22 +1372,22 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1441,16 +1411,16 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1479,22 +1449,22 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1556,22 +1526,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1592,7 +1562,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1604,7 +1574,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1633,22 +1603,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1669,19 +1639,19 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1710,22 +1680,22 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1746,7 +1716,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1755,13 +1725,13 @@
         <v>5</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1787,22 +1757,22 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1823,19 +1793,19 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>9</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -1864,22 +1834,22 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1900,19 +1870,19 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>9</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -1941,22 +1911,22 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1986,10 +1956,10 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2018,22 +1988,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2060,13 +2030,13 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>9</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2095,22 +2065,22 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2131,19 +2101,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>10</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>10</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2172,22 +2142,22 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2208,19 +2178,19 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>10</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2249,22 +2219,22 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2285,19 +2255,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>9</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2326,22 +2296,22 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2368,16 +2338,16 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2403,22 +2373,22 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2439,19 +2409,19 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2480,22 +2450,22 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2516,7 +2486,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2528,10 +2498,10 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2557,22 +2527,22 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2593,19 +2563,19 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>5</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2634,22 +2604,22 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2670,7 +2640,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2682,7 +2652,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2711,22 +2681,22 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2747,19 +2717,19 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>10</v>
       </c>
       <c r="V29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>10</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -2788,22 +2758,22 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2827,7 +2797,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>5</v>
@@ -2836,10 +2806,10 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2865,22 +2835,22 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2904,16 +2874,16 @@
         <v>9</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>5</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>6</v>
@@ -2942,22 +2912,22 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2978,10 +2948,10 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -2990,7 +2960,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3019,22 +2989,22 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3061,16 +3031,16 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3265,37 +3235,37 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3324,7 +3294,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -3342,7 +3312,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3383,7 +3353,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>94.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -3392,16 +3362,16 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M7">
         <v>100</v>
       </c>
       <c r="N7">
-        <v>94.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3410,10 +3380,10 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3442,37 +3412,37 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>89.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
-        <v>89.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3501,37 +3471,37 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>95</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M9">
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P9">
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>95</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3560,10 +3530,10 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3572,16 +3542,16 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3590,7 +3560,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3619,16 +3589,16 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>94.5</v>
+        <v>98.2</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -3637,16 +3607,16 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>94.5</v>
+        <v>98.2</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -3678,37 +3648,37 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J12">
-        <v>95.7</v>
+        <v>97.8</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L12">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P12">
-        <v>95.7</v>
+        <v>97.8</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R12">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3737,7 +3707,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>94.5</v>
+        <v>91.7</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -3746,7 +3716,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -3755,7 +3725,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>94.5</v>
+        <v>91.7</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -3764,7 +3734,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3796,10 +3766,10 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>81.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I14">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -3808,16 +3778,16 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>81.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="O14">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -3826,7 +3796,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -3855,13 +3825,13 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I15">
         <v>100</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -3873,13 +3843,13 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O15">
         <v>100</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3914,7 +3884,7 @@
         <v>81.3</v>
       </c>
       <c r="H16">
-        <v>81.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -3923,16 +3893,16 @@
         <v>95.7</v>
       </c>
       <c r="K16">
-        <v>85</v>
+        <v>85.7</v>
       </c>
       <c r="L16">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M16">
-        <v>81.3</v>
+        <v>56.3</v>
       </c>
       <c r="N16">
-        <v>81.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -3941,13 +3911,13 @@
         <v>95.7</v>
       </c>
       <c r="Q16">
-        <v>85</v>
+        <v>85.7</v>
       </c>
       <c r="R16">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S16">
-        <v>81.3</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3973,37 +3943,37 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>89.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J17">
         <v>95.7</v>
       </c>
       <c r="K17">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="L17">
-        <v>90</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
-        <v>89.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P17">
         <v>95.7</v>
       </c>
       <c r="Q17">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="R17">
-        <v>90</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -4035,13 +4005,13 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J18">
-        <v>95.7</v>
+        <v>97.8</v>
       </c>
       <c r="K18">
-        <v>95</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -4053,13 +4023,13 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P18">
-        <v>95.7</v>
+        <v>97.8</v>
       </c>
       <c r="Q18">
-        <v>95</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -4103,7 +4073,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -4121,7 +4091,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -4150,37 +4120,37 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="K20">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q20">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -4209,37 +4179,37 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M21">
         <v>100</v>
       </c>
       <c r="N21">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -4268,7 +4238,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>94.5</v>
+        <v>97.2</v>
       </c>
       <c r="I22">
         <v>100</v>
@@ -4277,16 +4247,16 @@
         <v>95.7</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
-        <v>94.5</v>
+        <v>97.2</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -4295,10 +4265,10 @@
         <v>95.7</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4327,37 +4297,37 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>94.5</v>
+        <v>97.2</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J23">
         <v>95.7</v>
       </c>
       <c r="K23">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M23">
         <v>100</v>
       </c>
       <c r="N23">
-        <v>94.5</v>
+        <v>97.2</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P23">
         <v>95.7</v>
       </c>
       <c r="Q23">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4389,10 +4359,10 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J24">
-        <v>95.7</v>
+        <v>97.8</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4407,10 +4377,10 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P24">
-        <v>95.7</v>
+        <v>97.8</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -4504,13 +4474,13 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>98.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I26">
         <v>100</v>
       </c>
       <c r="J26">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -4522,13 +4492,13 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>98.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O26">
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4563,40 +4533,40 @@
         <v>37.5</v>
       </c>
       <c r="H27">
-        <v>81.8</v>
+        <v>85.3</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J27">
         <v>95.7</v>
       </c>
       <c r="K27">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L27">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M27">
-        <v>37.5</v>
+        <v>68.8</v>
       </c>
       <c r="N27">
-        <v>81.8</v>
+        <v>85.3</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P27">
         <v>95.7</v>
       </c>
       <c r="Q27">
-        <v>90</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R27">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S27">
-        <v>37.5</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4622,7 +4592,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I28">
         <v>100</v>
@@ -4640,7 +4610,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -4681,10 +4651,10 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J29">
         <v>95.7</v>
@@ -4699,10 +4669,10 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P29">
         <v>95.7</v>
@@ -4746,13 +4716,13 @@
         <v>93.8</v>
       </c>
       <c r="J30">
-        <v>95.7</v>
+        <v>93.5</v>
       </c>
       <c r="K30">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L30">
-        <v>95</v>
+        <v>87.8</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -4764,13 +4734,13 @@
         <v>93.8</v>
       </c>
       <c r="P30">
-        <v>95.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q30">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R30">
-        <v>95</v>
+        <v>87.8</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -4799,40 +4769,40 @@
         <v>62.5</v>
       </c>
       <c r="H31">
-        <v>87.3</v>
+        <v>86.2</v>
       </c>
       <c r="I31">
         <v>93.8</v>
       </c>
       <c r="J31">
-        <v>95.7</v>
+        <v>93.5</v>
       </c>
       <c r="K31">
-        <v>85</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L31">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="M31">
-        <v>62.5</v>
+        <v>81.3</v>
       </c>
       <c r="N31">
-        <v>87.3</v>
+        <v>86.2</v>
       </c>
       <c r="O31">
         <v>93.8</v>
       </c>
       <c r="P31">
-        <v>95.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q31">
-        <v>85</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="R31">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="S31">
-        <v>62.5</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4858,37 +4828,37 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>89.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="J32">
-        <v>95.7</v>
+        <v>93.5</v>
       </c>
       <c r="K32">
-        <v>85</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L32">
-        <v>95</v>
+        <v>90.2</v>
       </c>
       <c r="M32">
         <v>100</v>
       </c>
       <c r="N32">
-        <v>89.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="P32">
-        <v>95.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q32">
-        <v>85</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="R32">
-        <v>95</v>
+        <v>90.2</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -4917,7 +4887,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>100</v>
+        <v>90.8</v>
       </c>
       <c r="I33">
         <v>100</v>
@@ -4926,16 +4896,16 @@
         <v>95.7</v>
       </c>
       <c r="K33">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M33">
         <v>100</v>
       </c>
       <c r="N33">
-        <v>100</v>
+        <v>90.8</v>
       </c>
       <c r="O33">
         <v>100</v>
@@ -4944,10 +4914,10 @@
         <v>95.7</v>
       </c>
       <c r="Q33">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5016,19 +4986,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5039,7 +5009,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5048,19 +5018,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="G3" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5071,7 +5041,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5080,19 +5050,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="G4" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5103,7 +5073,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5112,16 +5082,16 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H5">
         <v>8.800000000000001</v>
@@ -5135,7 +5105,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5156,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5167,7 +5137,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -5188,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5238,7 +5208,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5270,16 +5240,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920298</v>
+        <v>22330051920370</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
         <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5293,22 +5263,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920302</v>
+        <v>22330051920370</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5316,16 +5286,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920304</v>
+        <v>22330051920314</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -5339,22 +5309,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920305</v>
+        <v>22330051920314</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5362,16 +5332,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920312</v>
+        <v>22330051920305</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5385,16 +5355,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920364</v>
+        <v>22330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5408,16 +5378,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920370</v>
+        <v>22330051920397</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5426,52 +5396,6 @@
         <v>54</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920397</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920314</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ASV - Estadisticos 20232.xlsx
+++ b/grupos/4ASV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="75">
   <si>
     <t>Materia</t>
   </si>
@@ -182,18 +182,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Sanchez Hernández Raymundo</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>León González Ruth</t>
   </si>
   <si>
@@ -212,43 +212,37 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
+    <t>JARED DE JESUS</t>
   </si>
   <si>
     <t>MIRIAM AIMAR</t>
   </si>
   <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
     <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
   </si>
 </sst>
 </file>
@@ -774,40 +768,40 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>9</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>7</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -851,40 +845,40 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>9</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -928,40 +922,40 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>10</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1005,40 +999,40 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1082,22 +1076,22 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1106,16 +1100,16 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1159,40 +1153,40 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>9</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>8</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1236,25 +1230,25 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1269,7 +1263,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1313,25 +1307,25 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1340,13 +1334,13 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1390,37 +1384,37 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>7</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1467,22 +1461,22 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1500,7 +1494,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1544,22 +1538,22 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1571,13 +1565,13 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1621,37 +1615,37 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>10</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1698,34 +1692,34 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>5</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>5</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -1775,22 +1769,22 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1799,7 +1793,7 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -1852,28 +1846,28 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -1885,7 +1879,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1929,37 +1923,37 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>10</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2006,40 +2000,40 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>10</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2083,40 +2077,40 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2160,22 +2154,22 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2187,7 +2181,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2237,31 +2231,31 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>9</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2270,7 +2264,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2314,28 +2308,28 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2344,10 +2338,10 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2391,22 +2385,22 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2421,7 +2415,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2468,22 +2462,22 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2492,10 +2486,10 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2545,40 +2539,40 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2622,22 +2616,22 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2699,25 +2693,25 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -2726,10 +2720,10 @@
         <v>7</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -2776,37 +2770,37 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>9</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>9</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>5</v>
@@ -2853,22 +2847,22 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -2877,16 +2871,16 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2930,25 +2924,25 @@
         <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -2960,7 +2954,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3007,22 +3001,22 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3031,16 +3025,16 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>8</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3253,19 +3247,19 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O5">
-        <v>95.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P5">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q5">
-        <v>91.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R5">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3312,7 +3306,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3371,7 +3365,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>88.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3380,10 +3374,10 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>94.3</v>
+        <v>91.3</v>
       </c>
       <c r="R7">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3430,19 +3424,19 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>95.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="O8">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>91.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="R8">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3489,19 +3483,19 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>99.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="O9">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P9">
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>88.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="R9">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3548,10 +3542,10 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>98.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O10">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3560,7 +3554,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3607,19 +3601,19 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>98.2</v>
+        <v>94.3</v>
       </c>
       <c r="O11">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>97.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3666,19 +3660,19 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O12">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P12">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q12">
-        <v>97.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="R12">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3725,7 +3719,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>91.7</v>
+        <v>90.3</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -3734,10 +3728,10 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -3784,10 +3778,10 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>89.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="O14">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -3796,7 +3790,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -3843,19 +3837,19 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O15">
         <v>100</v>
       </c>
       <c r="P15">
+        <v>98.5</v>
+      </c>
+      <c r="Q15">
         <v>97.8</v>
       </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
       <c r="R15">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3902,22 +3896,22 @@
         <v>56.3</v>
       </c>
       <c r="N16">
-        <v>65.09999999999999</v>
+        <v>40.6</v>
       </c>
       <c r="O16">
         <v>100</v>
       </c>
       <c r="P16">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q16">
-        <v>85.7</v>
+        <v>84.8</v>
       </c>
       <c r="R16">
-        <v>95.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S16">
-        <v>56.3</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3961,19 +3955,19 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>89.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="O17">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P17">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="Q17">
-        <v>94.3</v>
+        <v>91.3</v>
       </c>
       <c r="R17">
-        <v>95.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -4023,16 +4017,16 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P18">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q18">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4079,19 +4073,19 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19">
+        <v>97</v>
+      </c>
+      <c r="Q19">
         <v>95.7</v>
       </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
       <c r="R19">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -4138,19 +4132,19 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>84.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q20">
-        <v>94.3</v>
+        <v>93.5</v>
       </c>
       <c r="R20">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -4197,19 +4191,19 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>96.3</v>
+        <v>97.7</v>
       </c>
       <c r="O21">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="R21">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -4256,19 +4250,19 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="Q22">
-        <v>97.09999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="R22">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4315,19 +4309,19 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>97.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O23">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P23">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="Q23">
-        <v>91.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R23">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4377,16 +4371,16 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P24">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4445,7 +4439,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4492,13 +4486,13 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O26">
         <v>100</v>
       </c>
       <c r="P26">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4551,22 +4545,22 @@
         <v>68.8</v>
       </c>
       <c r="N27">
-        <v>85.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="O27">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="P27">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="Q27">
-        <v>91.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R27">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S27">
-        <v>68.8</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4610,7 +4604,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>98.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -4669,13 +4663,13 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>95.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O29">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P29">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -4728,19 +4722,19 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>94.5</v>
+        <v>92</v>
       </c>
       <c r="O30">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="P30">
-        <v>93.5</v>
+        <v>95.5</v>
       </c>
       <c r="Q30">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R30">
-        <v>87.8</v>
+        <v>90.5</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -4787,22 +4781,22 @@
         <v>81.3</v>
       </c>
       <c r="N31">
-        <v>86.2</v>
+        <v>84</v>
       </c>
       <c r="O31">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="P31">
-        <v>93.5</v>
+        <v>94</v>
       </c>
       <c r="Q31">
-        <v>82.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R31">
-        <v>92.7</v>
+        <v>93.7</v>
       </c>
       <c r="S31">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4846,19 +4840,19 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>84.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="O32">
-        <v>92.2</v>
+        <v>94.8</v>
       </c>
       <c r="P32">
-        <v>93.5</v>
+        <v>95.5</v>
       </c>
       <c r="Q32">
-        <v>82.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R32">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -4905,19 +4899,19 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>90.8</v>
+        <v>92</v>
       </c>
       <c r="O33">
         <v>100</v>
       </c>
       <c r="P33">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="Q33">
-        <v>94.3</v>
+        <v>91.3</v>
       </c>
       <c r="R33">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -4977,7 +4971,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -4986,19 +4980,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="G2" s="2">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5009,7 +5003,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5030,7 +5024,7 @@
         <v>6.7</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5041,7 +5035,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5050,19 +5044,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="G4" s="2">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5073,7 +5067,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5094,7 +5088,7 @@
         <v>3.3</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5126,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5158,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5208,7 +5202,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5240,19 +5234,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920370</v>
+        <v>22330051920312</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>54</v>
@@ -5266,10 +5260,10 @@
         <v>22330051920370</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
         <v>72</v>
@@ -5278,7 +5272,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5286,19 +5280,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920314</v>
+        <v>22330051920397</v>
       </c>
       <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
         <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
       </c>
       <c r="D4" t="s">
         <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
@@ -5312,90 +5306,21 @@
         <v>22330051920314</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>55</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920305</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920312</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920397</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>
